--- a/PJT1.xlsx
+++ b/PJT1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAN-Notebook\Desktop\PJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA492FED-A35E-462A-BBB7-A12C799CD6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4201A99-80F2-4181-9923-A9D38102997A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,6 +59,7 @@
   </si>
   <si>
     <t>vs code c#. Проект PJT1. Необходимо создать отдельный класс DataBD с данными текстовыми для переменных Tagname Loop Comment, далее создать репозиторий для класса DataBD, далее создать метод для открытия файла excel для чтения двух первых полей в репозиторий. Далее создать форму FormDB с меню для открытие файла excel, Ручное добавление, удаление записей, очистка данных. Считанные данные выводить пе середине формы выводить считанные данные.
+Добавить модуль сохранения в формате txt файла.
 Весь код описать подробными комментариями для понимания C#</t>
   </si>
 </sst>
@@ -162,8 +163,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>200645</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>5886</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>364</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -538,7 +539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>3</v>
       </c>

--- a/PJT1.xlsx
+++ b/PJT1.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAN-Notebook\Desktop\PJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4201A99-80F2-4181-9923-A9D38102997A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939E5B6D-105B-491B-B9C7-A32F75B3F784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Задание" sheetId="2" r:id="rId2"/>
+    <sheet name="Class IoPoint" sheetId="3" r:id="rId3"/>
+    <sheet name="Id (Identification) class" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="359">
   <si>
     <t># Для работы с Excel файлами (.xlsx)</t>
   </si>
@@ -61,18 +63,1083 @@
     <t>vs code c#. Проект PJT1. Необходимо создать отдельный класс DataBD с данными текстовыми для переменных Tagname Loop Comment, далее создать репозиторий для класса DataBD, далее создать метод для открытия файла excel для чтения двух первых полей в репозиторий. Далее создать форму FormDB с меню для открытие файла excel, Ручное добавление, удаление записей, очистка данных. Считанные данные выводить пе середине формы выводить считанные данные.
 Добавить модуль сохранения в формате txt файла.
 Весь код описать подробными комментариями для понимания C#</t>
+  </si>
+  <si>
+    <t>IoPoint</t>
+  </si>
+  <si>
+    <t>using System.Collections.Generic;</t>
+  </si>
+  <si>
+    <t>/// &lt;summary&gt;</t>
+  </si>
+  <si>
+    <t>/// Точка ввода-вывода (I/O Point) для систем автоматизации.</t>
+  </si>
+  <si>
+    <t>/// Поддерживает DCS (распределенное управление), SCS/SIS (системы безопасности) и GDS (газообнаружение).</t>
+  </si>
+  <si>
+    <t>/// &lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t>public class IoPoint</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификационные данные точки (тег, контур, номер)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Identification Id { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Технологические параметры сигнала (тип прибора, место установки, взрывозащита)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Signal Signal { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Диапазоны измерений и уставки аварийной сигнализации&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Ranges Ranges { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Данные о кабельном хозяйстве (кабель, цвет, длина, маршрут)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Cable Cable { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Привязка к оборудованию контроллера (шкафы, стойки, модули, каналы)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Controller Hardware { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Информация о версиях и ревизиях документации&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Revision Rev { get; set; }</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>// ================================================================</t>
+  </si>
+  <si>
+    <t>/// Тип системы управления, к которой относится сигнал</t>
+  </si>
+  <si>
+    <t>public enum SystemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Распределенная система управления (основной техпроцесс)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DCS,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Система безопасности / SIS (Safety Instrumented System)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SCS,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Система обнаружения газа (Gas Detection System)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    GDS</t>
+  </si>
+  <si>
+    <t>/// Идентификация точки ввода-вывода</t>
+  </si>
+  <si>
+    <t>public class Identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Порядковый номер строки в списке (из колонки "Код")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int? No { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер технологической установки/зоны (например, 1401, 1402)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int? Area { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Технологический контур (LOOP) - связывает точки одного процесса&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Loop { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Типовой номер или модель устройства (TYPNO, например SDO0001-01)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Type { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер контура управления (может совпадать с Loop)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? LoopNo { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Логические номера для программирования (могут быть перечислены через "/")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? LogicNo { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Уникальный тег устройства (главный идентификатор, ОБЯЗАТЕЛЬНОЕ ПОЛЕ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Используется в документации, монтажных схемах и программе контроллера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string Tag { get; set; }</t>
+  </si>
+  <si>
+    <t>/// Технологические параметры сигнала</t>
+  </si>
+  <si>
+    <t>public class Signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Технологическое описание сигнала (например, "Styrene Inlet Switch Valve of 2701-TK-1205A")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Service { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Тип прибора/устройства (например, "Solenoid valve", "Temperature Transmitter")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? InstType { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификатор системы управления (FCS, например "2000-S-SC-B01")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Sys { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Тип системы: DCS (управление), SCS (безопасность) или GDS (газообнаружение)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public SystemType? SysType { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер листа P&amp;ID (Piping and Instrumentation Diagram)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Pid { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Место установки/подключения сигнала:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - Field: полевое оборудование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - SIS: внутри системы безопасности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - MCC: шкаф мотор-контроллеров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - AUX: вспомогательное оборудование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - GDS: система газообнаружения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Loc { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Тип сигнала (I/O Type):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - DOR-P: дискретный выход, питание от системы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - DIR(I)-NAMUR: дискретный вход, NAMUR датчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - S: софт-сигнал (внутри контроллера)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - AIR-LP: аналоговый вход, петля питания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - AIR(I)-LP: аналоговый вход, искробезопасный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - DIR-VFC: дискретный вход, сухой контакт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? SigType { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Взрывозащита оборудования:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - Ex.d: взрывонепроницаемая оболочка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - Ex.i: искробезопасная цепь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// - "-": не требуется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Ex { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификатор подсистемы (например, номер стойки или шкафа)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? SubSys { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Вспомогательный прибор (например, сигнальный изолятор, преобразователь)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Указывается, если сигнал проходит через дополнительное устройство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Aux { get; set; }</t>
+  </si>
+  <si>
+    <t>/// Диапазоны измерений и уставки аварийной сигнализации</t>
+  </si>
+  <si>
+    <t>public class Ranges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Основной диапазон измерения (обязательный, по умолчанию 0-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Используется для масштабирования сигнала в системе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Range Primary { get; set; } = new();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Вторичный диапазон измерения (опционально)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Может использоваться для пересчета в другие единицы (например, давление → уровень)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Range? Secondary { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Уставки аварийной сигнализации (LL, L, H, HH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Применяются для генерации предупреждений и отключений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Alarm? Alarms { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Единица измерения для уставок (если отличается от единицы Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? AlarmUnit { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Диапазон измерения (Min/Max) с единицей измерения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Всегда инициализируется с значениями по умолчанию 0-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public class Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Минимальное значение диапазона (по умолчанию 0)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal Min { get; set; } = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Максимальное значение диапазона (по умолчанию 100)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal Max { get; set; } = 100;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Единица измерения (мм, kPa, ℃, %VOL, μs/cm, PH, и т.д.)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Unit { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Уставки аварийной сигнализации (классические LL, L, H, HH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Используются для систем безопасности и предупреждения оператора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public class Alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Авария "Нижний-Нижний" - самый критичный низкий уровень (остановка)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal? LL { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Предупредительная авария "Нижний" (внимание оператора)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal? L { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Предупредительная авария "Верхний" (внимание оператора)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal? H { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Авария "Верхний-Верхний" - самый критичный высокий уровень (остановка)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public decimal? HH { get; set; }</t>
+  </si>
+  <si>
+    <t>/// Кабельное хозяйство - информация о физическом подключении сигнала</t>
+  </si>
+  <si>
+    <t>public class Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Уникальный идентификатор кабеля (по проектной документации)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Id { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Описание кабеля (назначение, куда подключен)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Desc { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Полный тип кабеля (например, "NH-KYJVP3 37x2.5mm2")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Включает количество и сечение жил, изоляцию, оболочку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Обозначение кабеля по проектной документации&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Desig { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Начальная точка кабеля (откуда идет, например "2701-S-JB-D018")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? From { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Конечная точка кабеля (куда идет, например "SIS")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? To { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Длина кабеля в метрах (целое число)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int? Len { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Цвет кабеля или цвет изоляции жилы (BK - черный, BU - синий)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Color { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер пары или жилы внутри кабеля&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int? Pair { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Дополнительное примечание по кабелю (изменения, особые условия)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Note { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Наименование кабеля по документации Aker Solutions&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? TitleAker { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер барабана для учета кабеля при монтаже&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Drum { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Напряжение питания для активных устройств (если применимо)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Volt { get; set; }</t>
+  </si>
+  <si>
+    <t>/// Оборудование контроллера - привязка сигнала к аппаратным средствам</t>
+  </si>
+  <si>
+    <t>public class Controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификатор кабеля по документации TECON (подрядчик)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? CableTecon { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер подстанции MCC (Motor Control Center) для моторных сигналов&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Mcc { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификатор шкафа управления (Control Cabinet)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? CtrlCab { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Идентификатор шкафа маршаллинга (Marshalling Cabinet) - промежуточные клеммы&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? MarshCab { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Тег процессора (CPU) в системе управления&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Cpu { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Информация о шасси (стойках) контроллера&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Chassis? Chassis { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Информация о модуле ввода-вывода (I/O Module)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Module? Module { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Шасси (стойка) контроллера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Может быть основной и резервный для горячего резервирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public class Chassis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор основного шасси (стойки)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Main { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор резервного шасси (стойки) для отказоустойчивости&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Red { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Модуль ввода-вывода (I/O Module)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// Содержит информацию о слотах, каналах и типе модуля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public class Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Номер слота основного модуля (например, A11, A13)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Slot { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Номер слота резервного модуля (например, A12, A14)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? SlotRed { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор основного модуля 1 (для двухканальных модулей)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Main1 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор основного модуля 2 (для двухканальных модулей)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Main2 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор резервного модуля 1&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Red1 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Идентификатор резервного модуля 2&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Red2 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;Номер канала внутри модуля (например, 20, 21)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public int? Ch { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// Тип модуля ввода-вывода:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// - DI32: дискретный вход, 32 канала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// - DO32P: дискретный выход, 32 канала, с питанием</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// - AI16H: аналоговый вход, 16 каналов, с HART протоколом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /// &lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        public string? Type { get; set; }</t>
+  </si>
+  <si>
+    <t>/// Управление версиями документации и ревизиями</t>
+  </si>
+  <si>
+    <t>public class Revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Номер ревизии (версия данных)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Подробное описание изменений в текущей ревизии&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Оборудование поставщика (пакетное оборудование, например "SDPump", "VINCI")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Package { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Дополнительное поле 1 (может содержать имя поставщика, например "Xinhui")&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Field1 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Дополнительное поле 2&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Field2 { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Ссылка на техническую документацию (номер документа, статус)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Doc { get; set; }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /// &lt;summary&gt;Ревизия от Aker Solutions (если применимо)&lt;/summary&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string? Aker { get; set; }</t>
+  </si>
+  <si>
+    <t>│</t>
+  </si>
+  <si>
+    <t>├── Id (Identification)</t>
+  </si>
+  <si>
+    <t>│   ├── No (int?)</t>
+  </si>
+  <si>
+    <t>│   ├── Area (int?)</t>
+  </si>
+  <si>
+    <t>│   ├── Loop (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Type (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── LoopNo (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── LogicNo (string?)</t>
+  </si>
+  <si>
+    <t>├── Signal (Signal)</t>
+  </si>
+  <si>
+    <t>│   ├── Service (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── InstType (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Sys (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── SysType (SystemType?) ⬅️ DCS | SCS | GDS</t>
+  </si>
+  <si>
+    <t>│   ├── Pid (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Loc (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── SigType (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Ex (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── SubSys (string?)</t>
+  </si>
+  <si>
+    <t>│   └── Aux (string?)</t>
+  </si>
+  <si>
+    <t>├── Ranges (Ranges)</t>
+  </si>
+  <si>
+    <t>│   ├── Primary (Range) ⬅️ ОБЯЗАТЕЛЬНОЕ (Min=0, Max=100)</t>
+  </si>
+  <si>
+    <t>│   │   ├── Min (decimal) = 0</t>
+  </si>
+  <si>
+    <t>│   │   ├── Max (decimal) = 100</t>
+  </si>
+  <si>
+    <t>│   │   └── Unit (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Secondary (Range?)</t>
+  </si>
+  <si>
+    <t>│   │   ├── Min (decimal)</t>
+  </si>
+  <si>
+    <t>│   │   ├── Max (decimal)</t>
+  </si>
+  <si>
+    <t>│   ├── Alarms (Alarm?)</t>
+  </si>
+  <si>
+    <t>│   │   ├── LL (decimal?)</t>
+  </si>
+  <si>
+    <t>│   │   ├── L (decimal?)</t>
+  </si>
+  <si>
+    <t>│   │   ├── H (decimal?)</t>
+  </si>
+  <si>
+    <t>│   │   └── HH (decimal?)</t>
+  </si>
+  <si>
+    <t>│   └── AlarmUnit (string?)</t>
+  </si>
+  <si>
+    <t>├── Cable (Cable)</t>
+  </si>
+  <si>
+    <t>│   ├── Id (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Desc (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Desig (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── From (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── To (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Len (int?)</t>
+  </si>
+  <si>
+    <t>│   ├── Color (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Pair (int?)</t>
+  </si>
+  <si>
+    <t>│   ├── Note (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── TitleAker (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Drum (string?)</t>
+  </si>
+  <si>
+    <t>│   └── Volt (string?)</t>
+  </si>
+  <si>
+    <t>├── Hardware (Controller)</t>
+  </si>
+  <si>
+    <t>│   ├── CableTecon (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Mcc (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── CtrlCab (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── MarshCab (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Cpu (string?)</t>
+  </si>
+  <si>
+    <t>│   ├── Chassis (Chassis?)</t>
+  </si>
+  <si>
+    <t>│   │   ├── Main (string?)</t>
+  </si>
+  <si>
+    <t>│   │   └── Red (string?)</t>
+  </si>
+  <si>
+    <t>│   └── Module (Module?)</t>
+  </si>
+  <si>
+    <t>│       ├── Slot (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── SlotRed (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── Main1 (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── Main2 (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── Red1 (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── Red2 (string?)</t>
+  </si>
+  <si>
+    <t>│       ├── Ch (int?)</t>
+  </si>
+  <si>
+    <t>│       └── Type (string?)</t>
+  </si>
+  <si>
+    <t>└── Rev (Revision)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── No (int?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── Desc (string?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── Package (string?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── Field1 (string?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── Field2 (string?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── Doc (string?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    └── Aker (string?)</t>
+  </si>
+  <si>
+    <t>Класс IoPoint</t>
+  </si>
+  <si>
+    <t>Сводка по обязательности полей</t>
+  </si>
+  <si>
+    <t>Класс</t>
+  </si>
+  <si>
+    <t>Поле</t>
+  </si>
+  <si>
+    <t>Обязательное</t>
+  </si>
+  <si>
+    <t>Значение по умолчанию</t>
+  </si>
+  <si>
+    <t>Identification</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ДА</t>
+    </r>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Остальные</t>
+  </si>
+  <si>
+    <t>❌ Нет</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Ranges</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>new Range()</t>
+  </si>
+  <si>
+    <t>Ranges.Range</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Все</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>│   └── Tag (string) ⬅️ ОБЯЗАТЕЛЬНОЕ. Уникальный тег устройства (главный ID)	2701-XZY-10101A	✅ Всегда</t>
+  </si>
+  <si>
+    <t>Назначение</t>
+  </si>
+  <si>
+    <t>Пример</t>
+  </si>
+  <si>
+    <t>Обязательность</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Порядковый номер строки в списке</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Номер установки/зоны (географическое)</t>
+  </si>
+  <si>
+    <t>Номер установки/зоны (функциональное)</t>
+  </si>
+  <si>
+    <t>Loop</t>
+  </si>
+  <si>
+    <t>2701-XZY-10101A</t>
+  </si>
+  <si>
+    <t>2701-XV-10101A</t>
+  </si>
+  <si>
+    <t>Технологический контур (функциональное разделение)</t>
+  </si>
+  <si>
+    <t>2701-X-10101A</t>
+  </si>
+  <si>
+    <t>Технологический контур (технологическое разделение)</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>2701-X-10105A</t>
+  </si>
+  <si>
+    <t>iLoop</t>
+  </si>
+  <si>
+    <t>Loop_pc</t>
+  </si>
+  <si>
+    <t>Вложенный (субконтур) Loop</t>
+  </si>
+  <si>
+    <t>Уникальный тег устройства (главный ID)</t>
+  </si>
+  <si>
+    <t>Tag_pc</t>
+  </si>
+  <si>
+    <t>Обычно</t>
+  </si>
+  <si>
+    <t>Технологический тэг устройства</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Styrene Inlet Switch Valve</t>
+  </si>
+  <si>
+    <t>Технологическое описание (RU)</t>
+  </si>
+  <si>
+    <t>Тип прибора (RU)</t>
+  </si>
+  <si>
+    <t>Распределительный клапан для впуска стирола</t>
+  </si>
+  <si>
+    <t>Электромагнитный клапан</t>
+  </si>
+  <si>
+    <t>Service_Eng</t>
+  </si>
+  <si>
+    <t>InstrumentType</t>
+  </si>
+  <si>
+    <t>InstrumentTypeEng</t>
+  </si>
+  <si>
+    <t>Тип прибора (ENG)</t>
+  </si>
+  <si>
+    <t>Технологическое описание (ENG)</t>
+  </si>
+  <si>
+    <t>Solenoid valve</t>
+  </si>
+  <si>
+    <t>Sys</t>
+  </si>
+  <si>
+    <t>DCS</t>
+  </si>
+  <si>
+    <t>Тип системы управления, к которой относится сигнал: public enum (DCS, SIS, GDS, "")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -100,13 +1167,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -121,11 +1207,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -133,6 +1219,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,47 +1586,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="47.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="23.5">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -517,13 +1639,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BF8950-189B-4CA4-A352-F0B4DF7D2EB2}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="5"/>
     <col min="2" max="2" width="73.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="58">
       <c r="A1" s="5">
         <v>1</v>
       </c>
@@ -531,7 +1653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="72.5">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -539,7 +1661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="116">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -551,4 +1673,2178 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFE76D8-CA53-4B09-B92C-BA1DA3DF0772}">
+  <dimension ref="A1:F472"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="93.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23.5">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29">
+      <c r="A6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB42329-15DC-4615-8DF9-5D4EB10C216A}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="23.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="23.7265625" style="5"/>
+    <col min="2" max="2" width="74.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="9">
+        <v>45</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" s="15">
+        <v>1400</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1401</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>